--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925250</v>
       </c>
       <c r="B2" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133925260</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925250</v>
       </c>
       <c r="B2" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133925260</v>
       </c>
       <c r="B3" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925250</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133925260</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925250</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133925260</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133925250</v>
+        <v>133925260</v>
       </c>
       <c r="B2" t="n">
-        <v>98053</v>
+        <v>80488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499198</v>
+        <v>499118</v>
       </c>
       <c r="R2" t="n">
-        <v>6620637</v>
+        <v>6620705</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133925260</v>
+        <v>133925250</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>98060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499118</v>
+        <v>499198</v>
       </c>
       <c r="R3" t="n">
-        <v>6620705</v>
+        <v>6620637</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135076302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,8 +1036,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25096-2026 artfynd.xlsx
+++ b/artfynd/A 25096-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135076302</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
